--- a/ONCHO/Entomological survey Survey/Nigeria/2026/kaduna/sites.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/kaduna/sites.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\kaduna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B18407-193F-43CB-AE14-7B18BAD6524D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE233E1-3FA1-4B17-A1E1-BB9508673D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC9477FD-2967-4060-A58D-FB783E564DCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="61">
   <si>
     <t>CHIKUN</t>
   </si>
@@ -67,13 +67,163 @@
   </si>
   <si>
     <t>UNGWAN PAH</t>
+  </si>
+  <si>
+    <t>IGABI</t>
+  </si>
+  <si>
+    <t>MASHIGI</t>
+  </si>
+  <si>
+    <t>OLD AFAKA</t>
+  </si>
+  <si>
+    <t>SABON GIDA KAKAUA</t>
+  </si>
+  <si>
+    <t>MAKARFI</t>
+  </si>
+  <si>
+    <t>ABA MALLAM</t>
+  </si>
+  <si>
+    <t>UNGWAN TUDU</t>
+  </si>
+  <si>
+    <t>KUBAU</t>
+  </si>
+  <si>
+    <t>UNGWAN KAKALE</t>
+  </si>
+  <si>
+    <t>SABON GARI</t>
+  </si>
+  <si>
+    <t>KATANGA</t>
+  </si>
+  <si>
+    <t>SAKADADI</t>
+  </si>
+  <si>
+    <t>KUDAN</t>
+  </si>
+  <si>
+    <t>UNGWAN DANKALA</t>
+  </si>
+  <si>
+    <t>SOBA</t>
+  </si>
+  <si>
+    <t>SANBIRNA</t>
+  </si>
+  <si>
+    <t>SOBA TOWN</t>
+  </si>
+  <si>
+    <t>JAJA A</t>
+  </si>
+  <si>
+    <t>ZANGON KATAF</t>
+  </si>
+  <si>
+    <t>UNGWAN YAKI (FANSIL)</t>
+  </si>
+  <si>
+    <t>KACHIA</t>
+  </si>
+  <si>
+    <t>IKKA MALLAM</t>
+  </si>
+  <si>
+    <t>AMUSE</t>
+  </si>
+  <si>
+    <t>GURARA</t>
+  </si>
+  <si>
+    <t>KUDANDAN (AGWA)</t>
+  </si>
+  <si>
+    <t>TSAUNIN KURA</t>
+  </si>
+  <si>
+    <t>KUJAMA GBAGYI</t>
+  </si>
+  <si>
+    <t>GAJILO</t>
+  </si>
+  <si>
+    <t>KWARAU</t>
+  </si>
+  <si>
+    <t>ZARIA</t>
+  </si>
+  <si>
+    <t>PAMMADINNA</t>
+  </si>
+  <si>
+    <t>IKARA</t>
+  </si>
+  <si>
+    <t>MABUGA</t>
+  </si>
+  <si>
+    <t>KAURU</t>
+  </si>
+  <si>
+    <t>KATURI VILLAGE</t>
+  </si>
+  <si>
+    <t>KIZAZA</t>
+  </si>
+  <si>
+    <t>KIWALLO KWARE</t>
+  </si>
+  <si>
+    <t>GIDAN MANA</t>
+  </si>
+  <si>
+    <t>MAI DAMISHI</t>
+  </si>
+  <si>
+    <t>UNGWAN ABAYA</t>
+  </si>
+  <si>
+    <t>LERE</t>
+  </si>
+  <si>
+    <t>KUDARU</t>
+  </si>
+  <si>
+    <t>TAREMU</t>
+  </si>
+  <si>
+    <t>KOBONKA</t>
+  </si>
+  <si>
+    <t>KABOB KAJUNGA</t>
+  </si>
+  <si>
+    <t>DEBODE</t>
+  </si>
+  <si>
+    <t>ATIYE</t>
+  </si>
+  <si>
+    <t>BAKIN KASUWA</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>KADUNA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +241,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -133,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -142,12 +300,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -477,122 +648,680 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F68C0F8-9F2E-49C5-AA35-54E6853C709C}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3">
+        <v>164</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="3">
+        <v>166</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
+        <v>146</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="3">
+        <v>165</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
         <v>141</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3">
+        <v>167</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3">
+        <v>168</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3">
+        <v>144</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3">
+        <v>145</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="3">
+        <v>170</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="3">
+        <v>161</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="3">
+        <v>181</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3">
+        <v>174</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="3">
+        <v>160</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="3">
+        <v>175</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D17" s="3">
         <v>144</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="F17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D21" s="3">
         <v>142</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C38" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
+      <c r="D38" s="3">
         <v>143</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="3">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C5">
-    <sortCondition ref="A2:A5"/>
-    <sortCondition ref="B2:B5"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D41">
+    <sortCondition ref="B2:B41"/>
+    <sortCondition ref="C2:C41"/>
   </sortState>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>